--- a/output/pdf_financials_xlsx/AXO.xlsx
+++ b/output/pdf_financials_xlsx/AXO.xlsx
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.191466</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.325793</v>
       </c>
     </row>
     <row r="65">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="68">
